--- a/data/trans_dic/P57B_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P57B_R-Clase-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con bienestar emocional por debajo del percentil 15 (Bericat)</t>
+          <t>Población con peor bienestar socioemocional (percentil 15) (Bericat) (tasa de respuesta: 98,25%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,8; 9,5</t>
+          <t>4,9; 9,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,46; 9,87</t>
+          <t>5,68; 10,09</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,86; 9,01</t>
+          <t>5,9; 8,97</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,27; 11,11</t>
+          <t>5,37; 10,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,69; 12,71</t>
+          <t>7,86; 12,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,17; 10,82</t>
+          <t>7,01; 10,59</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,14; 10,07</t>
+          <t>1,92; 9,79</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,08; 19,87</t>
+          <t>10,95; 19,38</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,16; 11,31</t>
+          <t>3,38; 11,44</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,55; 14,23</t>
+          <t>10,29; 14,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,67; 12,71</t>
+          <t>4,6; 12,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,62; 12,58</t>
+          <t>7,05; 12,72</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>13,89; 20,2</t>
+          <t>13,67; 20,06</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14,79; 23,0</t>
+          <t>14,67; 22,99</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15,09; 20,91</t>
+          <t>15,07; 20,92</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,86; 9,3</t>
+          <t>1,69; 9,59</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14,83; 19,31</t>
+          <t>14,84; 19,27</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11,76; 15,68</t>
+          <t>11,94; 16,12</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,51; 10,75</t>
+          <t>7,21; 10,74</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>11,08; 14,94</t>
+          <t>10,88; 14,83</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9,89; 12,56</t>
+          <t>9,96; 12,59</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con bienestar emocional por debajo del percentil 15 (Bericat)</t>
+          <t>Población con peor bienestar socioemocional (percentil 15) (Bericat) (tasa de respuesta: 98,25%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>24034; 47566</t>
+          <t>24557; 47903</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>24302; 43964</t>
+          <t>25284; 44927</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>55465; 85271</t>
+          <t>55784; 84858</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>23667; 49934</t>
+          <t>24109; 46414</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>29166; 48175</t>
+          <t>29799; 49222</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>59365; 89644</t>
+          <t>58105; 87689</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>14262; 67058</t>
+          <t>12819; 65192</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>18222; 32671</t>
+          <t>18013; 31869</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>26228; 93939</t>
+          <t>28036; 94973</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>107730; 145314</t>
+          <t>105114; 144438</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>45307; 123224</t>
+          <t>44638; 121683</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>151694; 250480</t>
+          <t>140436; 253140</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>64482; 93783</t>
+          <t>63442; 93144</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>121737; 189306</t>
+          <t>120766; 189232</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>194218; 269162</t>
+          <t>193993; 269331</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4362; 21829</t>
+          <t>3976; 22501</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>109337; 142358</t>
+          <t>109448; 142105</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>114301; 152454</t>
+          <t>116075; 156697</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>250625; 358511</t>
+          <t>240572; 358255</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>389877; 525581</t>
+          <t>382726; 522009</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>677829; 860882</t>
+          <t>682778; 863400</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P57B_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P57B_R-Clase-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,41%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,9; 9,56</t>
+          <t>4,82; 9,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,68; 10,09</t>
+          <t>6,33; 10,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,9; 8,97</t>
+          <t>6,02; 9,32</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,5%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,37; 10,33</t>
+          <t>5,13; 10,17</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,86; 12,99</t>
+          <t>7,48; 12,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,01; 10,59</t>
+          <t>6,97; 10,55</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>10,18%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,92; 9,79</t>
+          <t>6,37; 11,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,95; 19,38</t>
+          <t>10,63; 18,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,38; 11,44</t>
+          <t>8,3; 12,5</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>12,09%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,29; 14,15</t>
+          <t>10,39; 14,18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,6; 12,55</t>
+          <t>10,34; 13,83</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,05; 12,72</t>
+          <t>10,97; 13,58</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>20,08%</t>
         </is>
       </c>
     </row>
@@ -772,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>13,67; 20,06</t>
+          <t>13,76; 19,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14,67; 22,99</t>
+          <t>19,83; 24,75</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15,07; 20,92</t>
+          <t>18,31; 22,09</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,85%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,69; 9,59</t>
+          <t>1,65; 9,48</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14,84; 19,27</t>
+          <t>14,51; 18,8</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11,94; 16,12</t>
+          <t>12,08; 15,79</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>12,58%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,21; 10,74</t>
+          <t>9,3; 11,36</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>10,88; 14,83</t>
+          <t>13,76; 15,7</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9,96; 12,59</t>
+          <t>11,86; 13,31</t>
         </is>
       </c>
     </row>
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>34670</t>
+          <t>36370</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>34217</t>
+          <t>40081</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>68887</t>
+          <t>76451</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>24557; 47903</t>
+          <t>26332; 50596</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>25284; 44927</t>
+          <t>30777; 52050</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>55784; 84858</t>
+          <t>62142; 96177</t>
         </is>
       </c>
     </row>
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>33334</t>
+          <t>34887</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>38049</t>
+          <t>41567</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>71383</t>
+          <t>76454</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>24109; 46414</t>
+          <t>24612; 48831</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>29799; 49222</t>
+          <t>31389; 52414</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>58105; 87689</t>
+          <t>62674; 94895</t>
         </is>
       </c>
     </row>
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>38164</t>
+          <t>40487</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>24245</t>
+          <t>26112</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>62408</t>
+          <t>66599</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>12819; 65192</t>
+          <t>29885; 53954</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>18013; 31869</t>
+          <t>19667; 34726</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>28036; 94973</t>
+          <t>54304; 81794</t>
         </is>
       </c>
     </row>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>124196</t>
+          <t>135572</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>91601</t>
+          <t>102450</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>215798</t>
+          <t>238022</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>105114; 144438</t>
+          <t>116026; 158355</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>44638; 121683</t>
+          <t>88142; 117820</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>140436; 253140</t>
+          <t>216021; 267394</t>
         </is>
       </c>
     </row>
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>77632</t>
+          <t>92708</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>161851</t>
+          <t>180845</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>239483</t>
+          <t>273553</t>
         </is>
       </c>
     </row>
@@ -1324,24 +1324,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>63442; 93144</t>
+          <t>76042; 110478</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>120766; 189232</t>
+          <t>160501; 200328</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>193993; 269331</t>
+          <t>249473; 300979</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>9533</t>
+          <t>9255</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>124697</t>
+          <t>136478</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>134230</t>
+          <t>145733</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3976; 22501</t>
+          <t>3826; 21987</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>109448; 142105</t>
+          <t>119014; 154206</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>116075; 156697</t>
+          <t>127141; 166181</t>
         </is>
       </c>
     </row>
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>317529</t>
+          <t>349278</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>474660</t>
+          <t>527533</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>792189</t>
+          <t>876811</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>240572; 358255</t>
+          <t>315918; 385998</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>382726; 522009</t>
+          <t>491622; 561072</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>682778; 863400</t>
+          <t>826747; 927314</t>
         </is>
       </c>
     </row>
